--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -19,12 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>bfhwbfjhw</t>
-  </si>
-  <si>
-    <t>fjsbnfjb</t>
+    <t>dev darinda</t>
   </si>
 </sst>
 </file>
@@ -342,17 +339,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>1</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="e">
+        <f>--- ka parinda</f>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
